--- a/SType3.xlsx
+++ b/SType3.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://icrafcifor-my.sharepoint.com/personal/d_bodro_landscapealliance_org/Documents/Documents/GitHub/RegEco-PADAGIMO-SOLUSI/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="8_{8352FCB5-3818-471B-95EA-A95253910025}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{21DC9B83-AE44-4EA6-AC07-8132DA4124F2}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="8_{8352FCB5-3818-471B-95EA-A95253910025}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{014AAD85-0EBA-40E0-BEF9-D8848B40C2A6}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{BCA274C9-EF1D-4263-A604-C30810D98A49}"/>
   </bookViews>
@@ -778,10 +778,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04A98039-D7EE-467B-AECA-2C919B69B7D3}">
-  <dimension ref="A1:AA14"/>
+  <dimension ref="A1:W14"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -851,20 +851,8 @@
       <c r="W1">
         <v>21</v>
       </c>
-      <c r="X1">
-        <v>22</v>
-      </c>
-      <c r="Y1">
-        <v>23</v>
-      </c>
-      <c r="Z1">
-        <v>24</v>
-      </c>
-      <c r="AA1">
-        <v>25</v>
-      </c>
     </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>7</v>
       </c>
@@ -934,20 +922,8 @@
       <c r="W2">
         <v>0.9</v>
       </c>
-      <c r="X2">
-        <v>0.9</v>
-      </c>
-      <c r="Y2">
-        <v>0.9</v>
-      </c>
-      <c r="Z2">
-        <v>0.9</v>
-      </c>
-      <c r="AA2">
-        <v>0.9</v>
-      </c>
     </row>
-    <row r="3" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>7</v>
       </c>
@@ -1017,20 +993,8 @@
       <c r="W3">
         <v>0.9</v>
       </c>
-      <c r="X3">
-        <v>0.9</v>
-      </c>
-      <c r="Y3">
-        <v>0.9</v>
-      </c>
-      <c r="Z3">
-        <v>0.9</v>
-      </c>
-      <c r="AA3">
-        <v>0.9</v>
-      </c>
     </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>7</v>
       </c>
@@ -1100,20 +1064,8 @@
       <c r="W4">
         <v>0.9</v>
       </c>
-      <c r="X4">
-        <v>0.9</v>
-      </c>
-      <c r="Y4">
-        <v>0.9</v>
-      </c>
-      <c r="Z4">
-        <v>0.9</v>
-      </c>
-      <c r="AA4">
-        <v>0.9</v>
-      </c>
     </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>8</v>
       </c>
@@ -1183,20 +1135,8 @@
       <c r="W5">
         <v>0.6</v>
       </c>
-      <c r="X5">
-        <v>0.9</v>
-      </c>
-      <c r="Y5">
-        <v>0.9</v>
-      </c>
-      <c r="Z5">
-        <v>0.9</v>
-      </c>
-      <c r="AA5">
-        <v>0.9</v>
-      </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>8</v>
       </c>
@@ -1266,20 +1206,8 @@
       <c r="W6">
         <v>0.6</v>
       </c>
-      <c r="X6">
-        <v>0.9</v>
-      </c>
-      <c r="Y6">
-        <v>0.9</v>
-      </c>
-      <c r="Z6">
-        <v>0.9</v>
-      </c>
-      <c r="AA6">
-        <v>0.9</v>
-      </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>8</v>
       </c>
@@ -1349,20 +1277,8 @@
       <c r="W7">
         <v>0.6</v>
       </c>
-      <c r="X7">
-        <v>0.9</v>
-      </c>
-      <c r="Y7">
-        <v>0.9</v>
-      </c>
-      <c r="Z7">
-        <v>0.9</v>
-      </c>
-      <c r="AA7">
-        <v>0.9</v>
-      </c>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>1</v>
       </c>
@@ -1432,20 +1348,8 @@
       <c r="W8">
         <v>0.5</v>
       </c>
-      <c r="X8">
-        <v>0.7</v>
-      </c>
-      <c r="Y8">
-        <v>0.7</v>
-      </c>
-      <c r="Z8">
-        <v>0.7</v>
-      </c>
-      <c r="AA8">
-        <v>0.7</v>
-      </c>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>1</v>
       </c>
@@ -1515,20 +1419,8 @@
       <c r="W9">
         <v>0.5</v>
       </c>
-      <c r="X9">
-        <v>0.7</v>
-      </c>
-      <c r="Y9">
-        <v>0.7</v>
-      </c>
-      <c r="Z9">
-        <v>0.7</v>
-      </c>
-      <c r="AA9">
-        <v>0.7</v>
-      </c>
     </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>1</v>
       </c>
@@ -1598,20 +1490,8 @@
       <c r="W10">
         <v>0.5</v>
       </c>
-      <c r="X10">
-        <v>0.7</v>
-      </c>
-      <c r="Y10">
-        <v>0.7</v>
-      </c>
-      <c r="Z10">
-        <v>0.7</v>
-      </c>
-      <c r="AA10">
-        <v>0.7</v>
-      </c>
     </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
@@ -1681,20 +1561,8 @@
       <c r="W11">
         <v>0.5</v>
       </c>
-      <c r="X11">
-        <v>0.7</v>
-      </c>
-      <c r="Y11">
-        <v>0.7</v>
-      </c>
-      <c r="Z11">
-        <v>0.8</v>
-      </c>
-      <c r="AA11">
-        <v>0.8</v>
-      </c>
     </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>10</v>
       </c>
@@ -1764,20 +1632,8 @@
       <c r="W12">
         <v>0.5</v>
       </c>
-      <c r="X12">
-        <v>0.7</v>
-      </c>
-      <c r="Y12">
-        <v>0.7</v>
-      </c>
-      <c r="Z12">
-        <v>0.8</v>
-      </c>
-      <c r="AA12">
-        <v>0.8</v>
-      </c>
     </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>11</v>
       </c>
@@ -1847,20 +1703,8 @@
       <c r="W13">
         <v>0.5</v>
       </c>
-      <c r="X13">
-        <v>0.7</v>
-      </c>
-      <c r="Y13">
-        <v>0.7</v>
-      </c>
-      <c r="Z13">
-        <v>0.8</v>
-      </c>
-      <c r="AA13">
-        <v>0.8</v>
-      </c>
     </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>11</v>
       </c>
@@ -1929,18 +1773,6 @@
       </c>
       <c r="W14">
         <v>0.5</v>
-      </c>
-      <c r="X14">
-        <v>0.7</v>
-      </c>
-      <c r="Y14">
-        <v>0.7</v>
-      </c>
-      <c r="Z14">
-        <v>0.8</v>
-      </c>
-      <c r="AA14">
-        <v>0.8</v>
       </c>
     </row>
   </sheetData>

--- a/SType3.xlsx
+++ b/SType3.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://icrafcifor-my.sharepoint.com/personal/d_bodro_landscapealliance_org/Documents/Documents/GitHub/RegEco-PADAGIMO-SOLUSI/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="8_{8352FCB5-3818-471B-95EA-A95253910025}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{014AAD85-0EBA-40E0-BEF9-D8848B40C2A6}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="8_{8352FCB5-3818-471B-95EA-A95253910025}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F17826D4-9FD1-4214-A618-370F6EE7787B}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{BCA274C9-EF1D-4263-A604-C30810D98A49}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" xr2:uid="{BCA274C9-EF1D-4263-A604-C30810D98A49}"/>
   </bookViews>
   <sheets>
     <sheet name="SType3" sheetId="1" r:id="rId1"/>
@@ -778,7 +778,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04A98039-D7EE-467B-AECA-2C919B69B7D3}">
-  <dimension ref="A1:W14"/>
+  <dimension ref="A1:W13"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:23" x14ac:dyDescent="0.3">
@@ -854,10 +854,10 @@
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A2">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="B2">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -869,66 +869,66 @@
         <v>0</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>1.4238814029245758E-4</v>
       </c>
       <c r="G2">
-        <v>0.1</v>
+        <v>1.943000311154952E-4</v>
       </c>
       <c r="H2">
-        <v>0.1</v>
+        <v>2.4621192193853282E-4</v>
       </c>
       <c r="I2">
-        <v>0.1</v>
+        <v>2.9812381276157041E-4</v>
       </c>
       <c r="J2">
-        <v>0.1</v>
+        <v>3.5003570358460801E-4</v>
       </c>
       <c r="K2">
-        <v>0.1</v>
+        <v>4.0194759440764566E-4</v>
       </c>
       <c r="L2">
-        <v>0.2</v>
+        <v>4.5385948523068325E-4</v>
       </c>
       <c r="M2">
-        <v>0.2</v>
+        <v>5.0577137605372084E-4</v>
       </c>
       <c r="N2">
-        <v>0.2</v>
+        <v>5.5768326687675844E-4</v>
       </c>
       <c r="O2">
-        <v>0.4</v>
+        <v>6.0959515769979603E-4</v>
       </c>
       <c r="P2">
-        <v>0.4</v>
+        <v>6.6150704852283363E-4</v>
       </c>
       <c r="Q2">
-        <v>0.5</v>
+        <v>7.1341893934587133E-4</v>
       </c>
       <c r="R2">
-        <v>0.5</v>
+        <v>7.6533083016890892E-4</v>
       </c>
       <c r="S2">
-        <v>0.6</v>
+        <v>8.1724272099194652E-4</v>
       </c>
       <c r="T2">
-        <v>0.7</v>
+        <v>8.6915461181498411E-4</v>
       </c>
       <c r="U2">
-        <v>0.7</v>
+        <v>9.2106650263802171E-4</v>
       </c>
       <c r="V2">
-        <v>0.7</v>
+        <v>9.729783934610593E-4</v>
       </c>
       <c r="W2">
-        <v>0.9</v>
+        <v>1.0248902842840968E-3</v>
       </c>
     </row>
     <row r="3" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A3">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="B3">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -940,66 +940,66 @@
         <v>0</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>-2.9143354396410359E-16</v>
       </c>
       <c r="G3">
-        <v>0.1</v>
+        <v>5.2880888806806553E-2</v>
       </c>
       <c r="H3">
-        <v>0.1</v>
+        <v>0.10576177761361338</v>
       </c>
       <c r="I3">
-        <v>0.1</v>
+        <v>0.15864266642042024</v>
       </c>
       <c r="J3">
-        <v>0.1</v>
+        <v>0.2115235552272271</v>
       </c>
       <c r="K3">
-        <v>0.1</v>
+        <v>0.2644044440340339</v>
       </c>
       <c r="L3">
-        <v>0.2</v>
+        <v>0.31728533284084076</v>
       </c>
       <c r="M3">
-        <v>0.2</v>
+        <v>0.37016622164764762</v>
       </c>
       <c r="N3">
-        <v>0.2</v>
+        <v>0.42304711045445448</v>
       </c>
       <c r="O3">
-        <v>0.4</v>
+        <v>0.47592799926126134</v>
       </c>
       <c r="P3">
-        <v>0.4</v>
+        <v>0.52880888806806814</v>
       </c>
       <c r="Q3">
-        <v>0.5</v>
+        <v>0.581689776874875</v>
       </c>
       <c r="R3">
-        <v>0.5</v>
+        <v>0.63457066568168186</v>
       </c>
       <c r="S3">
-        <v>0.6</v>
+        <v>0.68745155448848871</v>
       </c>
       <c r="T3">
-        <v>0.7</v>
+        <v>0.74033244329529557</v>
       </c>
       <c r="U3">
-        <v>0.7</v>
+        <v>0.79321333210210243</v>
       </c>
       <c r="V3">
-        <v>0.7</v>
+        <v>0.84609422090890929</v>
       </c>
       <c r="W3">
-        <v>0.9</v>
+        <v>0.89897510971571615</v>
       </c>
     </row>
     <row r="4" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A4">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B4">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -1011,66 +1011,66 @@
         <v>0</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>5.0000000000000027E-3</v>
       </c>
       <c r="G4">
-        <v>0.1</v>
+        <v>7.064642881764136E-3</v>
       </c>
       <c r="H4">
-        <v>0.1</v>
+        <v>9.1292857635282693E-3</v>
       </c>
       <c r="I4">
-        <v>0.1</v>
+        <v>1.1193928645292403E-2</v>
       </c>
       <c r="J4">
-        <v>0.1</v>
+        <v>1.3258571527056538E-2</v>
       </c>
       <c r="K4">
-        <v>0.1</v>
+        <v>1.532321440882067E-2</v>
       </c>
       <c r="L4">
-        <v>0.2</v>
+        <v>1.7387857290584806E-2</v>
       </c>
       <c r="M4">
-        <v>0.2</v>
+        <v>1.9452500172348938E-2</v>
       </c>
       <c r="N4">
-        <v>0.2</v>
+        <v>2.1517143054113071E-2</v>
       </c>
       <c r="O4">
-        <v>0.4</v>
+        <v>2.3581785935877207E-2</v>
       </c>
       <c r="P4">
-        <v>0.4</v>
+        <v>2.5646428817641339E-2</v>
       </c>
       <c r="Q4">
-        <v>0.5</v>
+        <v>2.7711071699405471E-2</v>
       </c>
       <c r="R4">
-        <v>0.5</v>
+        <v>2.9775714581169607E-2</v>
       </c>
       <c r="S4">
-        <v>0.6</v>
+        <v>3.184035746293374E-2</v>
       </c>
       <c r="T4">
-        <v>0.7</v>
+        <v>3.3905000344697872E-2</v>
       </c>
       <c r="U4">
-        <v>0.7</v>
+        <v>3.5969643226462011E-2</v>
       </c>
       <c r="V4">
-        <v>0.7</v>
+        <v>3.8034286108226137E-2</v>
       </c>
       <c r="W4">
-        <v>0.9</v>
+        <v>4.0098928989990276E-2</v>
       </c>
     </row>
     <row r="5" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A5">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B5">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="C5">
         <v>0</v>
@@ -1082,66 +1082,66 @@
         <v>0</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>5.000000000000001E-2</v>
       </c>
       <c r="G5">
-        <v>0.1</v>
+        <v>4.8731603530713742E-2</v>
       </c>
       <c r="H5">
-        <v>0.1</v>
+        <v>4.7463207061427468E-2</v>
       </c>
       <c r="I5">
-        <v>0.1</v>
+        <v>4.61948105921412E-2</v>
       </c>
       <c r="J5">
-        <v>0.3</v>
+        <v>4.4926414122854925E-2</v>
       </c>
       <c r="K5">
-        <v>0.3</v>
+        <v>4.3658017653568651E-2</v>
       </c>
       <c r="L5">
-        <v>0.3</v>
+        <v>4.2389621184282383E-2</v>
       </c>
       <c r="M5">
-        <v>0.3</v>
+        <v>4.1121224714996109E-2</v>
       </c>
       <c r="N5">
-        <v>0.3</v>
+        <v>3.9852828245709841E-2</v>
       </c>
       <c r="O5">
-        <v>0.4</v>
+        <v>3.8584431776423567E-2</v>
       </c>
       <c r="P5">
-        <v>0.4</v>
+        <v>3.7316035307137299E-2</v>
       </c>
       <c r="Q5">
-        <v>0.5</v>
+        <v>3.6047638837851025E-2</v>
       </c>
       <c r="R5">
-        <v>0.5</v>
+        <v>3.477924236856475E-2</v>
       </c>
       <c r="S5">
-        <v>0.5</v>
+        <v>3.3510845899278482E-2</v>
       </c>
       <c r="T5">
-        <v>0.6</v>
+        <v>3.2242449429992208E-2</v>
       </c>
       <c r="U5">
-        <v>0.6</v>
+        <v>3.0974052960705937E-2</v>
       </c>
       <c r="V5">
-        <v>0.6</v>
+        <v>2.9705656491419666E-2</v>
       </c>
       <c r="W5">
-        <v>0.6</v>
+        <v>2.8437260022133395E-2</v>
       </c>
     </row>
     <row r="6" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A6">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B6">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -1153,66 +1153,66 @@
         <v>0</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>9.9999999999998354E-3</v>
       </c>
       <c r="G6">
-        <v>0.1</v>
+        <v>5.8263528800454586E-2</v>
       </c>
       <c r="H6">
-        <v>0.1</v>
+        <v>0.10652705760090933</v>
       </c>
       <c r="I6">
-        <v>0.1</v>
+        <v>0.15479058640136409</v>
       </c>
       <c r="J6">
-        <v>0.3</v>
+        <v>0.20305411520181885</v>
       </c>
       <c r="K6">
-        <v>0.3</v>
+        <v>0.25131764400227358</v>
       </c>
       <c r="L6">
-        <v>0.3</v>
+        <v>0.29958117280272833</v>
       </c>
       <c r="M6">
-        <v>0.3</v>
+        <v>0.34784470160318309</v>
       </c>
       <c r="N6">
-        <v>0.3</v>
+        <v>0.39610823040363785</v>
       </c>
       <c r="O6">
-        <v>0.4</v>
+        <v>0.44437175920409261</v>
       </c>
       <c r="P6">
-        <v>0.4</v>
+        <v>0.49263528800454737</v>
       </c>
       <c r="Q6">
-        <v>0.5</v>
+        <v>0.54089881680500207</v>
       </c>
       <c r="R6">
-        <v>0.5</v>
+        <v>0.58916234560545688</v>
       </c>
       <c r="S6">
-        <v>0.5</v>
+        <v>0.63742587440591159</v>
       </c>
       <c r="T6">
-        <v>0.6</v>
+        <v>0.6856894032063664</v>
       </c>
       <c r="U6">
-        <v>0.6</v>
+        <v>0.7339529320068211</v>
       </c>
       <c r="V6">
-        <v>0.6</v>
+        <v>0.7822164608072758</v>
       </c>
       <c r="W6">
-        <v>0.6</v>
+        <v>0.83047998960773062</v>
       </c>
     </row>
     <row r="7" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A7">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B7">
-        <v>25</v>
+        <v>52</v>
       </c>
       <c r="C7">
         <v>0</v>
@@ -1224,66 +1224,66 @@
         <v>0</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>4.9999999999999901E-5</v>
       </c>
       <c r="G7">
-        <v>0.1</v>
+        <v>1.0493066942033634E-4</v>
       </c>
       <c r="H7">
-        <v>0.1</v>
+        <v>1.5986133884067277E-4</v>
       </c>
       <c r="I7">
-        <v>0.1</v>
+        <v>2.1479200826100923E-4</v>
       </c>
       <c r="J7">
-        <v>0.3</v>
+        <v>2.6972267768134568E-4</v>
       </c>
       <c r="K7">
-        <v>0.3</v>
+        <v>3.2465334710168208E-4</v>
       </c>
       <c r="L7">
-        <v>0.3</v>
+        <v>3.7958401652201854E-4</v>
       </c>
       <c r="M7">
-        <v>0.3</v>
+        <v>4.3451468594235499E-4</v>
       </c>
       <c r="N7">
-        <v>0.3</v>
+        <v>4.8944535536269145E-4</v>
       </c>
       <c r="O7">
-        <v>0.4</v>
+        <v>5.443760247830279E-4</v>
       </c>
       <c r="P7">
-        <v>0.4</v>
+        <v>5.9930669420336436E-4</v>
       </c>
       <c r="Q7">
-        <v>0.5</v>
+        <v>6.5423736362370071E-4</v>
       </c>
       <c r="R7">
-        <v>0.5</v>
+        <v>7.0916803304403716E-4</v>
       </c>
       <c r="S7">
-        <v>0.5</v>
+        <v>7.6409870246437362E-4</v>
       </c>
       <c r="T7">
-        <v>0.6</v>
+        <v>8.1902937188471007E-4</v>
       </c>
       <c r="U7">
-        <v>0.6</v>
+        <v>8.7396004130504653E-4</v>
       </c>
       <c r="V7">
-        <v>0.6</v>
+        <v>9.2889071072538298E-4</v>
       </c>
       <c r="W7">
-        <v>0.6</v>
+        <v>9.8382138014571933E-4</v>
       </c>
     </row>
     <row r="8" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A8">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="B8">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="C8">
         <v>0</v>
@@ -1295,66 +1295,66 @@
         <v>0</v>
       </c>
       <c r="F8">
-        <v>0</v>
+        <v>9.999999999999995E-2</v>
       </c>
       <c r="G8">
-        <v>0.1</v>
+        <v>0.1101363016352695</v>
       </c>
       <c r="H8">
-        <v>0.1</v>
+        <v>0.12027260327053904</v>
       </c>
       <c r="I8">
-        <v>0.1</v>
+        <v>0.13040890490580859</v>
       </c>
       <c r="J8">
-        <v>0.3</v>
+        <v>0.14054520654107813</v>
       </c>
       <c r="K8">
-        <v>0.3</v>
+        <v>0.15068150817634768</v>
       </c>
       <c r="L8">
-        <v>0.3</v>
+        <v>0.1608178098116172</v>
       </c>
       <c r="M8">
-        <v>0.3</v>
+        <v>0.17095411144688677</v>
       </c>
       <c r="N8">
-        <v>0.3</v>
+        <v>0.18109041308215629</v>
       </c>
       <c r="O8">
-        <v>0.4</v>
+        <v>0.19122671471742586</v>
       </c>
       <c r="P8">
-        <v>0.4</v>
+        <v>0.20136301635269538</v>
       </c>
       <c r="Q8">
-        <v>0.4</v>
+        <v>0.21149931798796492</v>
       </c>
       <c r="R8">
-        <v>0.4</v>
+        <v>0.22163561962323447</v>
       </c>
       <c r="S8">
-        <v>0.4</v>
+        <v>0.23177192125850402</v>
       </c>
       <c r="T8">
-        <v>0.5</v>
+        <v>0.24190822289377356</v>
       </c>
       <c r="U8">
-        <v>0.5</v>
+        <v>0.25204452452904313</v>
       </c>
       <c r="V8">
-        <v>0.5</v>
+        <v>0.26218082616431265</v>
       </c>
       <c r="W8">
-        <v>0.5</v>
+        <v>0.27231712779958217</v>
       </c>
     </row>
     <row r="9" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A9">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="B9">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="C9">
         <v>0</v>
@@ -1366,66 +1366,66 @@
         <v>0</v>
       </c>
       <c r="F9">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="G9">
-        <v>0.1</v>
+        <v>0.13037132417215724</v>
       </c>
       <c r="H9">
-        <v>0.1</v>
+        <v>0.16074264834431448</v>
       </c>
       <c r="I9">
-        <v>0.1</v>
+        <v>0.19111397251647172</v>
       </c>
       <c r="J9">
-        <v>0.3</v>
+        <v>0.22148529668862896</v>
       </c>
       <c r="K9">
-        <v>0.3</v>
+        <v>0.2518566208607862</v>
       </c>
       <c r="L9">
-        <v>0.3</v>
+        <v>0.28222794503294346</v>
       </c>
       <c r="M9">
-        <v>0.3</v>
+        <v>0.31259926920510067</v>
       </c>
       <c r="N9">
-        <v>0.3</v>
+        <v>0.34297059337725794</v>
       </c>
       <c r="O9">
-        <v>0.4</v>
+        <v>0.37334191754941515</v>
       </c>
       <c r="P9">
-        <v>0.4</v>
+        <v>0.40371324172157236</v>
       </c>
       <c r="Q9">
-        <v>0.4</v>
+        <v>0.43408456589372962</v>
       </c>
       <c r="R9">
-        <v>0.4</v>
+        <v>0.46445589006588689</v>
       </c>
       <c r="S9">
-        <v>0.4</v>
+        <v>0.4948272142380441</v>
       </c>
       <c r="T9">
-        <v>0.5</v>
+        <v>0.52519853841020137</v>
       </c>
       <c r="U9">
-        <v>0.5</v>
+        <v>0.55556986258235863</v>
       </c>
       <c r="V9">
-        <v>0.5</v>
+        <v>0.5859411867545159</v>
       </c>
       <c r="W9">
-        <v>0.5</v>
+        <v>0.61631251092667316</v>
       </c>
     </row>
     <row r="10" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A10">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="B10">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="C10">
         <v>0</v>
@@ -1437,66 +1437,66 @@
         <v>0</v>
       </c>
       <c r="F10">
-        <v>0</v>
+        <v>4.9999999999999984E-3</v>
       </c>
       <c r="G10">
-        <v>0.1</v>
+        <v>5.3747271337497068E-3</v>
       </c>
       <c r="H10">
-        <v>0.1</v>
+        <v>5.749454267499416E-3</v>
       </c>
       <c r="I10">
-        <v>0.1</v>
+        <v>6.1241814012491244E-3</v>
       </c>
       <c r="J10">
-        <v>0.3</v>
+        <v>6.4989085349988329E-3</v>
       </c>
       <c r="K10">
-        <v>0.3</v>
+        <v>6.8736356687485421E-3</v>
       </c>
       <c r="L10">
-        <v>0.3</v>
+        <v>7.2483628024982505E-3</v>
       </c>
       <c r="M10">
-        <v>0.3</v>
+        <v>7.6230899362479589E-3</v>
       </c>
       <c r="N10">
-        <v>0.3</v>
+        <v>7.9978170699976682E-3</v>
       </c>
       <c r="O10">
-        <v>0.4</v>
+        <v>8.3725442037473757E-3</v>
       </c>
       <c r="P10">
-        <v>0.4</v>
+        <v>8.747271337497085E-3</v>
       </c>
       <c r="Q10">
-        <v>0.4</v>
+        <v>9.1219984712467943E-3</v>
       </c>
       <c r="R10">
-        <v>0.4</v>
+        <v>9.4967256049965018E-3</v>
       </c>
       <c r="S10">
-        <v>0.4</v>
+        <v>9.8714527387462111E-3</v>
       </c>
       <c r="T10">
-        <v>0.5</v>
+        <v>1.024617987249592E-2</v>
       </c>
       <c r="U10">
-        <v>0.5</v>
+        <v>1.0620907006245628E-2</v>
       </c>
       <c r="V10">
-        <v>0.5</v>
+        <v>1.0995634139995335E-2</v>
       </c>
       <c r="W10">
-        <v>0.5</v>
+        <v>1.1370361273745045E-2</v>
       </c>
     </row>
     <row r="11" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A11">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="B11">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="C11">
         <v>0</v>
@@ -1505,69 +1505,69 @@
         <v>0</v>
       </c>
       <c r="E11">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="F11">
-        <v>0.3</v>
+        <v>0.10000000000000009</v>
       </c>
       <c r="G11">
-        <v>0.3</v>
+        <v>0.14232835094533447</v>
       </c>
       <c r="H11">
-        <v>0.3</v>
+        <v>0.18465670189066882</v>
       </c>
       <c r="I11">
-        <v>0.3</v>
+        <v>0.2269850528360032</v>
       </c>
       <c r="J11">
-        <v>0.3</v>
+        <v>0.26931340378133761</v>
       </c>
       <c r="K11">
-        <v>0.3</v>
+        <v>0.31164175472667194</v>
       </c>
       <c r="L11">
-        <v>0.4</v>
+        <v>0.35397010567200632</v>
       </c>
       <c r="M11">
-        <v>0.4</v>
+        <v>0.3962984566173407</v>
       </c>
       <c r="N11">
-        <v>0.4</v>
+        <v>0.43862680756267508</v>
       </c>
       <c r="O11">
-        <v>0.4</v>
+        <v>0.48095515850800946</v>
       </c>
       <c r="P11">
-        <v>0.4</v>
+        <v>0.5232835094533439</v>
       </c>
       <c r="Q11">
-        <v>0.5</v>
+        <v>0.56561186039867817</v>
       </c>
       <c r="R11">
-        <v>0.5</v>
+        <v>0.60794021134401255</v>
       </c>
       <c r="S11">
-        <v>0.5</v>
+        <v>0.65026856228934693</v>
       </c>
       <c r="T11">
-        <v>0.5</v>
+        <v>0.69259691323468131</v>
       </c>
       <c r="U11">
-        <v>0.5</v>
+        <v>0.73492526418001569</v>
       </c>
       <c r="V11">
-        <v>0.5</v>
+        <v>0.77725361512535007</v>
       </c>
       <c r="W11">
-        <v>0.5</v>
+        <v>0.81958196607068445</v>
       </c>
     </row>
     <row r="12" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A12">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="B12">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="C12">
         <v>0</v>
@@ -1576,69 +1576,69 @@
         <v>0</v>
       </c>
       <c r="E12">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="F12">
-        <v>0.3</v>
+        <v>9.9999999999999985E-3</v>
       </c>
       <c r="G12">
-        <v>0.3</v>
+        <v>1.3644973990486751E-2</v>
       </c>
       <c r="H12">
-        <v>0.3</v>
+        <v>1.7289947980973504E-2</v>
       </c>
       <c r="I12">
-        <v>0.3</v>
+        <v>2.0934921971460258E-2</v>
       </c>
       <c r="J12">
-        <v>0.3</v>
+        <v>2.4579895961947013E-2</v>
       </c>
       <c r="K12">
-        <v>0.3</v>
+        <v>2.8224869952433763E-2</v>
       </c>
       <c r="L12">
-        <v>0.4</v>
+        <v>3.1869843942920514E-2</v>
       </c>
       <c r="M12">
-        <v>0.4</v>
+        <v>3.5514817933407272E-2</v>
       </c>
       <c r="N12">
-        <v>0.4</v>
+        <v>3.9159791923894023E-2</v>
       </c>
       <c r="O12">
-        <v>0.4</v>
+        <v>4.2804765914380781E-2</v>
       </c>
       <c r="P12">
-        <v>0.4</v>
+        <v>4.6449739904867532E-2</v>
       </c>
       <c r="Q12">
-        <v>0.5</v>
+        <v>5.0094713895354283E-2</v>
       </c>
       <c r="R12">
-        <v>0.5</v>
+        <v>5.3739687885841041E-2</v>
       </c>
       <c r="S12">
-        <v>0.5</v>
+        <v>5.7384661876327792E-2</v>
       </c>
       <c r="T12">
-        <v>0.5</v>
+        <v>6.1029635866814549E-2</v>
       </c>
       <c r="U12">
-        <v>0.5</v>
+        <v>6.4674609857301307E-2</v>
       </c>
       <c r="V12">
-        <v>0.5</v>
+        <v>6.8319583847788051E-2</v>
       </c>
       <c r="W12">
-        <v>0.5</v>
+        <v>7.1964557838274795E-2</v>
       </c>
     </row>
     <row r="13" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A13">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="B13">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="C13">
         <v>0</v>
@@ -1647,132 +1647,61 @@
         <v>0</v>
       </c>
       <c r="E13">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="F13">
-        <v>0.3</v>
+        <v>4.9999999999999708E-4</v>
       </c>
       <c r="G13">
-        <v>0.3</v>
+        <v>9.6785153476709501E-4</v>
       </c>
       <c r="H13">
-        <v>0.3</v>
+        <v>1.4357030695341931E-3</v>
       </c>
       <c r="I13">
-        <v>0.3</v>
+        <v>1.9035546043012909E-3</v>
       </c>
       <c r="J13">
-        <v>0.3</v>
+        <v>2.3714061390683887E-3</v>
       </c>
       <c r="K13">
-        <v>0.3</v>
+        <v>2.839257673835487E-3</v>
       </c>
       <c r="L13">
-        <v>0.4</v>
+        <v>3.3071092086025848E-3</v>
       </c>
       <c r="M13">
-        <v>0.4</v>
+        <v>3.7749607433696826E-3</v>
       </c>
       <c r="N13">
-        <v>0.4</v>
+        <v>4.2428122781367804E-3</v>
       </c>
       <c r="O13">
-        <v>0.4</v>
+        <v>4.7106638129038782E-3</v>
       </c>
       <c r="P13">
-        <v>0.4</v>
+        <v>5.1785153476709761E-3</v>
       </c>
       <c r="Q13">
-        <v>0.5</v>
+        <v>5.6463668824380748E-3</v>
       </c>
       <c r="R13">
-        <v>0.5</v>
+        <v>6.1142184172051726E-3</v>
       </c>
       <c r="S13">
-        <v>0.5</v>
+        <v>6.5820699519722704E-3</v>
       </c>
       <c r="T13">
-        <v>0.5</v>
+        <v>7.0499214867393682E-3</v>
       </c>
       <c r="U13">
-        <v>0.5</v>
+        <v>7.517773021506466E-3</v>
       </c>
       <c r="V13">
-        <v>0.5</v>
+        <v>7.9856245562735656E-3</v>
       </c>
       <c r="W13">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A14">
-        <v>11</v>
-      </c>
-      <c r="B14">
-        <v>25</v>
-      </c>
-      <c r="C14">
-        <v>0</v>
-      </c>
-      <c r="D14">
-        <v>0</v>
-      </c>
-      <c r="E14">
-        <v>0.3</v>
-      </c>
-      <c r="F14">
-        <v>0.3</v>
-      </c>
-      <c r="G14">
-        <v>0.3</v>
-      </c>
-      <c r="H14">
-        <v>0.3</v>
-      </c>
-      <c r="I14">
-        <v>0.3</v>
-      </c>
-      <c r="J14">
-        <v>0.3</v>
-      </c>
-      <c r="K14">
-        <v>0.3</v>
-      </c>
-      <c r="L14">
-        <v>0.4</v>
-      </c>
-      <c r="M14">
-        <v>0.4</v>
-      </c>
-      <c r="N14">
-        <v>0.4</v>
-      </c>
-      <c r="O14">
-        <v>0.4</v>
-      </c>
-      <c r="P14">
-        <v>0.4</v>
-      </c>
-      <c r="Q14">
-        <v>0.5</v>
-      </c>
-      <c r="R14">
-        <v>0.5</v>
-      </c>
-      <c r="S14">
-        <v>0.5</v>
-      </c>
-      <c r="T14">
-        <v>0.5</v>
-      </c>
-      <c r="U14">
-        <v>0.5</v>
-      </c>
-      <c r="V14">
-        <v>0.5</v>
-      </c>
-      <c r="W14">
-        <v>0.5</v>
+        <v>8.4534760910406626E-3</v>
       </c>
     </row>
   </sheetData>

--- a/SType3.xlsx
+++ b/SType3.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://icrafcifor-my.sharepoint.com/personal/d_bodro_landscapealliance_org/Documents/Documents/GitHub/RegEco-PADAGIMO-SOLUSI/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="8_{8352FCB5-3818-471B-95EA-A95253910025}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F17826D4-9FD1-4214-A618-370F6EE7787B}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="8_{8352FCB5-3818-471B-95EA-A95253910025}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{85DC404A-7E4C-4BB1-8BD9-FC201651F405}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" xr2:uid="{BCA274C9-EF1D-4263-A604-C30810D98A49}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{BCA274C9-EF1D-4263-A604-C30810D98A49}"/>
   </bookViews>
   <sheets>
     <sheet name="SType3" sheetId="1" r:id="rId1"/>
@@ -869,58 +869,58 @@
         <v>0</v>
       </c>
       <c r="F2">
-        <v>1.4238814029245758E-4</v>
+        <v>0</v>
       </c>
       <c r="G2">
-        <v>1.943000311154952E-4</v>
+        <v>0.1</v>
       </c>
       <c r="H2">
-        <v>2.4621192193853282E-4</v>
+        <v>0.1</v>
       </c>
       <c r="I2">
-        <v>2.9812381276157041E-4</v>
+        <v>0.1</v>
       </c>
       <c r="J2">
-        <v>3.5003570358460801E-4</v>
+        <v>0.1</v>
       </c>
       <c r="K2">
-        <v>4.0194759440764566E-4</v>
+        <v>0.1</v>
       </c>
       <c r="L2">
-        <v>4.5385948523068325E-4</v>
+        <v>0.2</v>
       </c>
       <c r="M2">
-        <v>5.0577137605372084E-4</v>
+        <v>0.2</v>
       </c>
       <c r="N2">
-        <v>5.5768326687675844E-4</v>
+        <v>0.2</v>
       </c>
       <c r="O2">
-        <v>6.0959515769979603E-4</v>
+        <v>0.2</v>
       </c>
       <c r="P2">
-        <v>6.6150704852283363E-4</v>
+        <v>0.2</v>
       </c>
       <c r="Q2">
-        <v>7.1341893934587133E-4</v>
+        <v>0.5</v>
       </c>
       <c r="R2">
-        <v>7.6533083016890892E-4</v>
+        <v>0.5</v>
       </c>
       <c r="S2">
-        <v>8.1724272099194652E-4</v>
+        <v>0.5</v>
       </c>
       <c r="T2">
-        <v>8.6915461181498411E-4</v>
+        <v>0.5</v>
       </c>
       <c r="U2">
-        <v>9.2106650263802171E-4</v>
+        <v>0.5</v>
       </c>
       <c r="V2">
-        <v>9.729783934610593E-4</v>
+        <v>0.5</v>
       </c>
       <c r="W2">
-        <v>1.0248902842840968E-3</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="3" spans="1:23" x14ac:dyDescent="0.3">
@@ -940,58 +940,58 @@
         <v>0</v>
       </c>
       <c r="F3">
-        <v>-2.9143354396410359E-16</v>
+        <v>0</v>
       </c>
       <c r="G3">
-        <v>5.2880888806806553E-2</v>
+        <v>0.1</v>
       </c>
       <c r="H3">
-        <v>0.10576177761361338</v>
+        <v>0.1</v>
       </c>
       <c r="I3">
-        <v>0.15864266642042024</v>
+        <v>0.1</v>
       </c>
       <c r="J3">
-        <v>0.2115235552272271</v>
+        <v>0.1</v>
       </c>
       <c r="K3">
-        <v>0.2644044440340339</v>
+        <v>0.1</v>
       </c>
       <c r="L3">
-        <v>0.31728533284084076</v>
+        <v>0.2</v>
       </c>
       <c r="M3">
-        <v>0.37016622164764762</v>
+        <v>0.2</v>
       </c>
       <c r="N3">
-        <v>0.42304711045445448</v>
+        <v>0.2</v>
       </c>
       <c r="O3">
-        <v>0.47592799926126134</v>
+        <v>0.2</v>
       </c>
       <c r="P3">
-        <v>0.52880888806806814</v>
+        <v>0.2</v>
       </c>
       <c r="Q3">
-        <v>0.581689776874875</v>
+        <v>0.5</v>
       </c>
       <c r="R3">
-        <v>0.63457066568168186</v>
+        <v>0.5</v>
       </c>
       <c r="S3">
-        <v>0.68745155448848871</v>
+        <v>0.5</v>
       </c>
       <c r="T3">
-        <v>0.74033244329529557</v>
+        <v>0.5</v>
       </c>
       <c r="U3">
-        <v>0.79321333210210243</v>
+        <v>0.5</v>
       </c>
       <c r="V3">
-        <v>0.84609422090890929</v>
+        <v>0.5</v>
       </c>
       <c r="W3">
-        <v>0.89897510971571615</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="4" spans="1:23" x14ac:dyDescent="0.3">
@@ -1011,58 +1011,58 @@
         <v>0</v>
       </c>
       <c r="F4">
-        <v>5.0000000000000027E-3</v>
+        <v>0</v>
       </c>
       <c r="G4">
-        <v>7.064642881764136E-3</v>
+        <v>0.1</v>
       </c>
       <c r="H4">
-        <v>9.1292857635282693E-3</v>
+        <v>0.1</v>
       </c>
       <c r="I4">
-        <v>1.1193928645292403E-2</v>
+        <v>0.1</v>
       </c>
       <c r="J4">
-        <v>1.3258571527056538E-2</v>
+        <v>0.1</v>
       </c>
       <c r="K4">
-        <v>1.532321440882067E-2</v>
+        <v>0.1</v>
       </c>
       <c r="L4">
-        <v>1.7387857290584806E-2</v>
+        <v>0.2</v>
       </c>
       <c r="M4">
-        <v>1.9452500172348938E-2</v>
+        <v>0.2</v>
       </c>
       <c r="N4">
-        <v>2.1517143054113071E-2</v>
+        <v>0.2</v>
       </c>
       <c r="O4">
-        <v>2.3581785935877207E-2</v>
+        <v>0.2</v>
       </c>
       <c r="P4">
-        <v>2.5646428817641339E-2</v>
+        <v>0.2</v>
       </c>
       <c r="Q4">
-        <v>2.7711071699405471E-2</v>
+        <v>0.5</v>
       </c>
       <c r="R4">
-        <v>2.9775714581169607E-2</v>
+        <v>0.5</v>
       </c>
       <c r="S4">
-        <v>3.184035746293374E-2</v>
+        <v>0.5</v>
       </c>
       <c r="T4">
-        <v>3.3905000344697872E-2</v>
+        <v>0.5</v>
       </c>
       <c r="U4">
-        <v>3.5969643226462011E-2</v>
+        <v>0.5</v>
       </c>
       <c r="V4">
-        <v>3.8034286108226137E-2</v>
+        <v>0.5</v>
       </c>
       <c r="W4">
-        <v>4.0098928989990276E-2</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="5" spans="1:23" x14ac:dyDescent="0.3">
@@ -1082,58 +1082,58 @@
         <v>0</v>
       </c>
       <c r="F5">
-        <v>5.000000000000001E-2</v>
+        <v>0</v>
       </c>
       <c r="G5">
-        <v>4.8731603530713742E-2</v>
+        <v>0.1</v>
       </c>
       <c r="H5">
-        <v>4.7463207061427468E-2</v>
+        <v>0.1</v>
       </c>
       <c r="I5">
-        <v>4.61948105921412E-2</v>
+        <v>0.1</v>
       </c>
       <c r="J5">
-        <v>4.4926414122854925E-2</v>
+        <v>0.1</v>
       </c>
       <c r="K5">
-        <v>4.3658017653568651E-2</v>
+        <v>0.1</v>
       </c>
       <c r="L5">
-        <v>4.2389621184282383E-2</v>
+        <v>0.2</v>
       </c>
       <c r="M5">
-        <v>4.1121224714996109E-2</v>
+        <v>0.2</v>
       </c>
       <c r="N5">
-        <v>3.9852828245709841E-2</v>
+        <v>0.2</v>
       </c>
       <c r="O5">
-        <v>3.8584431776423567E-2</v>
+        <v>0.2</v>
       </c>
       <c r="P5">
-        <v>3.7316035307137299E-2</v>
+        <v>0.2</v>
       </c>
       <c r="Q5">
-        <v>3.6047638837851025E-2</v>
+        <v>0.5</v>
       </c>
       <c r="R5">
-        <v>3.477924236856475E-2</v>
+        <v>0.5</v>
       </c>
       <c r="S5">
-        <v>3.3510845899278482E-2</v>
+        <v>0.5</v>
       </c>
       <c r="T5">
-        <v>3.2242449429992208E-2</v>
+        <v>0.5</v>
       </c>
       <c r="U5">
-        <v>3.0974052960705937E-2</v>
+        <v>0.5</v>
       </c>
       <c r="V5">
-        <v>2.9705656491419666E-2</v>
+        <v>0.5</v>
       </c>
       <c r="W5">
-        <v>2.8437260022133395E-2</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="6" spans="1:23" x14ac:dyDescent="0.3">
@@ -1153,58 +1153,58 @@
         <v>0</v>
       </c>
       <c r="F6">
-        <v>9.9999999999998354E-3</v>
+        <v>0</v>
       </c>
       <c r="G6">
-        <v>5.8263528800454586E-2</v>
+        <v>0.1</v>
       </c>
       <c r="H6">
-        <v>0.10652705760090933</v>
+        <v>0.1</v>
       </c>
       <c r="I6">
-        <v>0.15479058640136409</v>
+        <v>0.1</v>
       </c>
       <c r="J6">
-        <v>0.20305411520181885</v>
+        <v>0.1</v>
       </c>
       <c r="K6">
-        <v>0.25131764400227358</v>
+        <v>0.1</v>
       </c>
       <c r="L6">
-        <v>0.29958117280272833</v>
+        <v>0.2</v>
       </c>
       <c r="M6">
-        <v>0.34784470160318309</v>
+        <v>0.2</v>
       </c>
       <c r="N6">
-        <v>0.39610823040363785</v>
+        <v>0.2</v>
       </c>
       <c r="O6">
-        <v>0.44437175920409261</v>
+        <v>0.2</v>
       </c>
       <c r="P6">
-        <v>0.49263528800454737</v>
+        <v>0.2</v>
       </c>
       <c r="Q6">
-        <v>0.54089881680500207</v>
+        <v>0.5</v>
       </c>
       <c r="R6">
-        <v>0.58916234560545688</v>
+        <v>0.5</v>
       </c>
       <c r="S6">
-        <v>0.63742587440591159</v>
+        <v>0.5</v>
       </c>
       <c r="T6">
-        <v>0.6856894032063664</v>
+        <v>0.5</v>
       </c>
       <c r="U6">
-        <v>0.7339529320068211</v>
+        <v>0.5</v>
       </c>
       <c r="V6">
-        <v>0.7822164608072758</v>
+        <v>0.5</v>
       </c>
       <c r="W6">
-        <v>0.83047998960773062</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="7" spans="1:23" x14ac:dyDescent="0.3">
@@ -1224,58 +1224,58 @@
         <v>0</v>
       </c>
       <c r="F7">
-        <v>4.9999999999999901E-5</v>
+        <v>0</v>
       </c>
       <c r="G7">
-        <v>1.0493066942033634E-4</v>
+        <v>0.1</v>
       </c>
       <c r="H7">
-        <v>1.5986133884067277E-4</v>
+        <v>0.1</v>
       </c>
       <c r="I7">
-        <v>2.1479200826100923E-4</v>
+        <v>0.1</v>
       </c>
       <c r="J7">
-        <v>2.6972267768134568E-4</v>
+        <v>0.1</v>
       </c>
       <c r="K7">
-        <v>3.2465334710168208E-4</v>
+        <v>0.1</v>
       </c>
       <c r="L7">
-        <v>3.7958401652201854E-4</v>
+        <v>0.2</v>
       </c>
       <c r="M7">
-        <v>4.3451468594235499E-4</v>
+        <v>0.2</v>
       </c>
       <c r="N7">
-        <v>4.8944535536269145E-4</v>
+        <v>0.2</v>
       </c>
       <c r="O7">
-        <v>5.443760247830279E-4</v>
+        <v>0.2</v>
       </c>
       <c r="P7">
-        <v>5.9930669420336436E-4</v>
+        <v>0.2</v>
       </c>
       <c r="Q7">
-        <v>6.5423736362370071E-4</v>
+        <v>0.5</v>
       </c>
       <c r="R7">
-        <v>7.0916803304403716E-4</v>
+        <v>0.5</v>
       </c>
       <c r="S7">
-        <v>7.6409870246437362E-4</v>
+        <v>0.5</v>
       </c>
       <c r="T7">
-        <v>8.1902937188471007E-4</v>
+        <v>0.5</v>
       </c>
       <c r="U7">
-        <v>8.7396004130504653E-4</v>
+        <v>0.5</v>
       </c>
       <c r="V7">
-        <v>9.2889071072538298E-4</v>
+        <v>0.5</v>
       </c>
       <c r="W7">
-        <v>9.8382138014571933E-4</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="8" spans="1:23" x14ac:dyDescent="0.3">
@@ -1295,58 +1295,58 @@
         <v>0</v>
       </c>
       <c r="F8">
-        <v>9.999999999999995E-2</v>
+        <v>0</v>
       </c>
       <c r="G8">
-        <v>0.1101363016352695</v>
+        <v>0.1</v>
       </c>
       <c r="H8">
-        <v>0.12027260327053904</v>
+        <v>0.1</v>
       </c>
       <c r="I8">
-        <v>0.13040890490580859</v>
+        <v>0.1</v>
       </c>
       <c r="J8">
-        <v>0.14054520654107813</v>
+        <v>0.1</v>
       </c>
       <c r="K8">
-        <v>0.15068150817634768</v>
+        <v>0.1</v>
       </c>
       <c r="L8">
-        <v>0.1608178098116172</v>
+        <v>0.2</v>
       </c>
       <c r="M8">
-        <v>0.17095411144688677</v>
+        <v>0.2</v>
       </c>
       <c r="N8">
-        <v>0.18109041308215629</v>
+        <v>0.2</v>
       </c>
       <c r="O8">
-        <v>0.19122671471742586</v>
+        <v>0.2</v>
       </c>
       <c r="P8">
-        <v>0.20136301635269538</v>
+        <v>0.2</v>
       </c>
       <c r="Q8">
-        <v>0.21149931798796492</v>
+        <v>0.5</v>
       </c>
       <c r="R8">
-        <v>0.22163561962323447</v>
+        <v>0.5</v>
       </c>
       <c r="S8">
-        <v>0.23177192125850402</v>
+        <v>0.5</v>
       </c>
       <c r="T8">
-        <v>0.24190822289377356</v>
+        <v>0.5</v>
       </c>
       <c r="U8">
-        <v>0.25204452452904313</v>
+        <v>0.5</v>
       </c>
       <c r="V8">
-        <v>0.26218082616431265</v>
+        <v>0.5</v>
       </c>
       <c r="W8">
-        <v>0.27231712779958217</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="9" spans="1:23" x14ac:dyDescent="0.3">
@@ -1366,58 +1366,58 @@
         <v>0</v>
       </c>
       <c r="F9">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="G9">
-        <v>0.13037132417215724</v>
+        <v>0.1</v>
       </c>
       <c r="H9">
-        <v>0.16074264834431448</v>
+        <v>0.1</v>
       </c>
       <c r="I9">
-        <v>0.19111397251647172</v>
+        <v>0.1</v>
       </c>
       <c r="J9">
-        <v>0.22148529668862896</v>
+        <v>0.1</v>
       </c>
       <c r="K9">
-        <v>0.2518566208607862</v>
+        <v>0.1</v>
       </c>
       <c r="L9">
-        <v>0.28222794503294346</v>
+        <v>0.2</v>
       </c>
       <c r="M9">
-        <v>0.31259926920510067</v>
+        <v>0.2</v>
       </c>
       <c r="N9">
-        <v>0.34297059337725794</v>
+        <v>0.2</v>
       </c>
       <c r="O9">
-        <v>0.37334191754941515</v>
+        <v>0.2</v>
       </c>
       <c r="P9">
-        <v>0.40371324172157236</v>
+        <v>0.2</v>
       </c>
       <c r="Q9">
-        <v>0.43408456589372962</v>
+        <v>0.5</v>
       </c>
       <c r="R9">
-        <v>0.46445589006588689</v>
+        <v>0.5</v>
       </c>
       <c r="S9">
-        <v>0.4948272142380441</v>
+        <v>0.5</v>
       </c>
       <c r="T9">
-        <v>0.52519853841020137</v>
+        <v>0.5</v>
       </c>
       <c r="U9">
-        <v>0.55556986258235863</v>
+        <v>0.5</v>
       </c>
       <c r="V9">
-        <v>0.5859411867545159</v>
+        <v>0.5</v>
       </c>
       <c r="W9">
-        <v>0.61631251092667316</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="10" spans="1:23" x14ac:dyDescent="0.3">
@@ -1437,58 +1437,58 @@
         <v>0</v>
       </c>
       <c r="F10">
-        <v>4.9999999999999984E-3</v>
+        <v>0</v>
       </c>
       <c r="G10">
-        <v>5.3747271337497068E-3</v>
+        <v>0.1</v>
       </c>
       <c r="H10">
-        <v>5.749454267499416E-3</v>
+        <v>0.1</v>
       </c>
       <c r="I10">
-        <v>6.1241814012491244E-3</v>
+        <v>0.1</v>
       </c>
       <c r="J10">
-        <v>6.4989085349988329E-3</v>
+        <v>0.1</v>
       </c>
       <c r="K10">
-        <v>6.8736356687485421E-3</v>
+        <v>0.1</v>
       </c>
       <c r="L10">
-        <v>7.2483628024982505E-3</v>
+        <v>0.2</v>
       </c>
       <c r="M10">
-        <v>7.6230899362479589E-3</v>
+        <v>0.2</v>
       </c>
       <c r="N10">
-        <v>7.9978170699976682E-3</v>
+        <v>0.2</v>
       </c>
       <c r="O10">
-        <v>8.3725442037473757E-3</v>
+        <v>0.2</v>
       </c>
       <c r="P10">
-        <v>8.747271337497085E-3</v>
+        <v>0.2</v>
       </c>
       <c r="Q10">
-        <v>9.1219984712467943E-3</v>
+        <v>0.5</v>
       </c>
       <c r="R10">
-        <v>9.4967256049965018E-3</v>
+        <v>0.5</v>
       </c>
       <c r="S10">
-        <v>9.8714527387462111E-3</v>
+        <v>0.5</v>
       </c>
       <c r="T10">
-        <v>1.024617987249592E-2</v>
+        <v>0.5</v>
       </c>
       <c r="U10">
-        <v>1.0620907006245628E-2</v>
+        <v>0.5</v>
       </c>
       <c r="V10">
-        <v>1.0995634139995335E-2</v>
+        <v>0.5</v>
       </c>
       <c r="W10">
-        <v>1.1370361273745045E-2</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="11" spans="1:23" x14ac:dyDescent="0.3">
@@ -1508,58 +1508,58 @@
         <v>0</v>
       </c>
       <c r="F11">
-        <v>0.10000000000000009</v>
+        <v>0</v>
       </c>
       <c r="G11">
-        <v>0.14232835094533447</v>
+        <v>0.1</v>
       </c>
       <c r="H11">
-        <v>0.18465670189066882</v>
+        <v>0.1</v>
       </c>
       <c r="I11">
-        <v>0.2269850528360032</v>
+        <v>0.1</v>
       </c>
       <c r="J11">
-        <v>0.26931340378133761</v>
+        <v>0.1</v>
       </c>
       <c r="K11">
-        <v>0.31164175472667194</v>
+        <v>0.1</v>
       </c>
       <c r="L11">
-        <v>0.35397010567200632</v>
+        <v>0.2</v>
       </c>
       <c r="M11">
-        <v>0.3962984566173407</v>
+        <v>0.2</v>
       </c>
       <c r="N11">
-        <v>0.43862680756267508</v>
+        <v>0.2</v>
       </c>
       <c r="O11">
-        <v>0.48095515850800946</v>
+        <v>0.2</v>
       </c>
       <c r="P11">
-        <v>0.5232835094533439</v>
+        <v>0.2</v>
       </c>
       <c r="Q11">
-        <v>0.56561186039867817</v>
+        <v>0.5</v>
       </c>
       <c r="R11">
-        <v>0.60794021134401255</v>
+        <v>0.5</v>
       </c>
       <c r="S11">
-        <v>0.65026856228934693</v>
+        <v>0.5</v>
       </c>
       <c r="T11">
-        <v>0.69259691323468131</v>
+        <v>0.5</v>
       </c>
       <c r="U11">
-        <v>0.73492526418001569</v>
+        <v>0.5</v>
       </c>
       <c r="V11">
-        <v>0.77725361512535007</v>
+        <v>0.5</v>
       </c>
       <c r="W11">
-        <v>0.81958196607068445</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="12" spans="1:23" x14ac:dyDescent="0.3">
@@ -1579,58 +1579,58 @@
         <v>0</v>
       </c>
       <c r="F12">
-        <v>9.9999999999999985E-3</v>
+        <v>0</v>
       </c>
       <c r="G12">
-        <v>1.3644973990486751E-2</v>
+        <v>0.1</v>
       </c>
       <c r="H12">
-        <v>1.7289947980973504E-2</v>
+        <v>0.1</v>
       </c>
       <c r="I12">
-        <v>2.0934921971460258E-2</v>
+        <v>0.1</v>
       </c>
       <c r="J12">
-        <v>2.4579895961947013E-2</v>
+        <v>0.1</v>
       </c>
       <c r="K12">
-        <v>2.8224869952433763E-2</v>
+        <v>0.1</v>
       </c>
       <c r="L12">
-        <v>3.1869843942920514E-2</v>
+        <v>0.2</v>
       </c>
       <c r="M12">
-        <v>3.5514817933407272E-2</v>
+        <v>0.2</v>
       </c>
       <c r="N12">
-        <v>3.9159791923894023E-2</v>
+        <v>0.2</v>
       </c>
       <c r="O12">
-        <v>4.2804765914380781E-2</v>
+        <v>0.2</v>
       </c>
       <c r="P12">
-        <v>4.6449739904867532E-2</v>
+        <v>0.2</v>
       </c>
       <c r="Q12">
-        <v>5.0094713895354283E-2</v>
+        <v>0.5</v>
       </c>
       <c r="R12">
-        <v>5.3739687885841041E-2</v>
+        <v>0.5</v>
       </c>
       <c r="S12">
-        <v>5.7384661876327792E-2</v>
+        <v>0.5</v>
       </c>
       <c r="T12">
-        <v>6.1029635866814549E-2</v>
+        <v>0.5</v>
       </c>
       <c r="U12">
-        <v>6.4674609857301307E-2</v>
+        <v>0.5</v>
       </c>
       <c r="V12">
-        <v>6.8319583847788051E-2</v>
+        <v>0.5</v>
       </c>
       <c r="W12">
-        <v>7.1964557838274795E-2</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="13" spans="1:23" x14ac:dyDescent="0.3">
@@ -1650,58 +1650,58 @@
         <v>0</v>
       </c>
       <c r="F13">
-        <v>4.9999999999999708E-4</v>
+        <v>0</v>
       </c>
       <c r="G13">
-        <v>9.6785153476709501E-4</v>
+        <v>0.1</v>
       </c>
       <c r="H13">
-        <v>1.4357030695341931E-3</v>
+        <v>0.1</v>
       </c>
       <c r="I13">
-        <v>1.9035546043012909E-3</v>
+        <v>0.1</v>
       </c>
       <c r="J13">
-        <v>2.3714061390683887E-3</v>
+        <v>0.1</v>
       </c>
       <c r="K13">
-        <v>2.839257673835487E-3</v>
+        <v>0.1</v>
       </c>
       <c r="L13">
-        <v>3.3071092086025848E-3</v>
+        <v>0.2</v>
       </c>
       <c r="M13">
-        <v>3.7749607433696826E-3</v>
+        <v>0.2</v>
       </c>
       <c r="N13">
-        <v>4.2428122781367804E-3</v>
+        <v>0.2</v>
       </c>
       <c r="O13">
-        <v>4.7106638129038782E-3</v>
+        <v>0.2</v>
       </c>
       <c r="P13">
-        <v>5.1785153476709761E-3</v>
+        <v>0.2</v>
       </c>
       <c r="Q13">
-        <v>5.6463668824380748E-3</v>
+        <v>0.5</v>
       </c>
       <c r="R13">
-        <v>6.1142184172051726E-3</v>
+        <v>0.5</v>
       </c>
       <c r="S13">
-        <v>6.5820699519722704E-3</v>
+        <v>0.5</v>
       </c>
       <c r="T13">
-        <v>7.0499214867393682E-3</v>
+        <v>0.5</v>
       </c>
       <c r="U13">
-        <v>7.517773021506466E-3</v>
+        <v>0.5</v>
       </c>
       <c r="V13">
-        <v>7.9856245562735656E-3</v>
+        <v>0.5</v>
       </c>
       <c r="W13">
-        <v>8.4534760910406626E-3</v>
+        <v>0.9</v>
       </c>
     </row>
   </sheetData>

--- a/SType3.xlsx
+++ b/SType3.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://icrafcifor-my.sharepoint.com/personal/d_bodro_landscapealliance_org/Documents/Documents/GitHub/RegEco-PADAGIMO-SOLUSI/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="8_{8352FCB5-3818-471B-95EA-A95253910025}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{85DC404A-7E4C-4BB1-8BD9-FC201651F405}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="8_{8352FCB5-3818-471B-95EA-A95253910025}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{56F26C9E-5709-4ECA-B093-F76370F06E4D}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{BCA274C9-EF1D-4263-A604-C30810D98A49}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{BCA274C9-EF1D-4263-A604-C30810D98A49}"/>
   </bookViews>
   <sheets>
     <sheet name="SType3" sheetId="1" r:id="rId1"/>
@@ -890,34 +890,34 @@
         <v>0.2</v>
       </c>
       <c r="M2">
-        <v>0.2</v>
+        <v>0.26363636363636367</v>
       </c>
       <c r="N2">
-        <v>0.2</v>
+        <v>0.32727272727272727</v>
       </c>
       <c r="O2">
-        <v>0.2</v>
+        <v>0.39090909090909093</v>
       </c>
       <c r="P2">
-        <v>0.2</v>
+        <v>0.45454545454545459</v>
       </c>
       <c r="Q2">
-        <v>0.5</v>
+        <v>0.51818181818181819</v>
       </c>
       <c r="R2">
-        <v>0.5</v>
+        <v>0.58181818181818179</v>
       </c>
       <c r="S2">
-        <v>0.5</v>
+        <v>0.6454545454545455</v>
       </c>
       <c r="T2">
-        <v>0.5</v>
+        <v>0.70909090909090911</v>
       </c>
       <c r="U2">
-        <v>0.5</v>
+        <v>0.77272727272727282</v>
       </c>
       <c r="V2">
-        <v>0.5</v>
+        <v>0.83636363636363642</v>
       </c>
       <c r="W2">
         <v>0.9</v>
@@ -961,34 +961,34 @@
         <v>0.2</v>
       </c>
       <c r="M3">
-        <v>0.2</v>
+        <v>0.26363636363636367</v>
       </c>
       <c r="N3">
-        <v>0.2</v>
+        <v>0.32727272727272727</v>
       </c>
       <c r="O3">
-        <v>0.2</v>
+        <v>0.39090909090909093</v>
       </c>
       <c r="P3">
-        <v>0.2</v>
+        <v>0.45454545454545459</v>
       </c>
       <c r="Q3">
-        <v>0.5</v>
+        <v>0.51818181818181819</v>
       </c>
       <c r="R3">
-        <v>0.5</v>
+        <v>0.58181818181818179</v>
       </c>
       <c r="S3">
-        <v>0.5</v>
+        <v>0.6454545454545455</v>
       </c>
       <c r="T3">
-        <v>0.5</v>
+        <v>0.70909090909090911</v>
       </c>
       <c r="U3">
-        <v>0.5</v>
+        <v>0.77272727272727282</v>
       </c>
       <c r="V3">
-        <v>0.5</v>
+        <v>0.83636363636363642</v>
       </c>
       <c r="W3">
         <v>0.9</v>
@@ -1032,34 +1032,34 @@
         <v>0.2</v>
       </c>
       <c r="M4">
-        <v>0.2</v>
+        <v>0.26363636363636367</v>
       </c>
       <c r="N4">
-        <v>0.2</v>
+        <v>0.32727272727272727</v>
       </c>
       <c r="O4">
-        <v>0.2</v>
+        <v>0.39090909090909093</v>
       </c>
       <c r="P4">
-        <v>0.2</v>
+        <v>0.45454545454545459</v>
       </c>
       <c r="Q4">
-        <v>0.5</v>
+        <v>0.51818181818181819</v>
       </c>
       <c r="R4">
-        <v>0.5</v>
+        <v>0.58181818181818179</v>
       </c>
       <c r="S4">
-        <v>0.5</v>
+        <v>0.6454545454545455</v>
       </c>
       <c r="T4">
-        <v>0.5</v>
+        <v>0.70909090909090911</v>
       </c>
       <c r="U4">
-        <v>0.5</v>
+        <v>0.77272727272727282</v>
       </c>
       <c r="V4">
-        <v>0.5</v>
+        <v>0.83636363636363642</v>
       </c>
       <c r="W4">
         <v>0.9</v>
@@ -1103,34 +1103,34 @@
         <v>0.2</v>
       </c>
       <c r="M5">
-        <v>0.2</v>
+        <v>0.26363636363636367</v>
       </c>
       <c r="N5">
-        <v>0.2</v>
+        <v>0.32727272727272727</v>
       </c>
       <c r="O5">
-        <v>0.2</v>
+        <v>0.39090909090909093</v>
       </c>
       <c r="P5">
-        <v>0.2</v>
+        <v>0.45454545454545459</v>
       </c>
       <c r="Q5">
-        <v>0.5</v>
+        <v>0.51818181818181819</v>
       </c>
       <c r="R5">
-        <v>0.5</v>
+        <v>0.58181818181818179</v>
       </c>
       <c r="S5">
-        <v>0.5</v>
+        <v>0.6454545454545455</v>
       </c>
       <c r="T5">
-        <v>0.5</v>
+        <v>0.70909090909090911</v>
       </c>
       <c r="U5">
-        <v>0.5</v>
+        <v>0.77272727272727282</v>
       </c>
       <c r="V5">
-        <v>0.5</v>
+        <v>0.83636363636363642</v>
       </c>
       <c r="W5">
         <v>0.9</v>
@@ -1174,34 +1174,34 @@
         <v>0.2</v>
       </c>
       <c r="M6">
-        <v>0.2</v>
+        <v>0.26363636363636367</v>
       </c>
       <c r="N6">
-        <v>0.2</v>
+        <v>0.32727272727272727</v>
       </c>
       <c r="O6">
-        <v>0.2</v>
+        <v>0.39090909090909093</v>
       </c>
       <c r="P6">
-        <v>0.2</v>
+        <v>0.45454545454545459</v>
       </c>
       <c r="Q6">
-        <v>0.5</v>
+        <v>0.51818181818181819</v>
       </c>
       <c r="R6">
-        <v>0.5</v>
+        <v>0.58181818181818179</v>
       </c>
       <c r="S6">
-        <v>0.5</v>
+        <v>0.6454545454545455</v>
       </c>
       <c r="T6">
-        <v>0.5</v>
+        <v>0.70909090909090911</v>
       </c>
       <c r="U6">
-        <v>0.5</v>
+        <v>0.77272727272727282</v>
       </c>
       <c r="V6">
-        <v>0.5</v>
+        <v>0.83636363636363642</v>
       </c>
       <c r="W6">
         <v>0.9</v>
@@ -1245,34 +1245,34 @@
         <v>0.2</v>
       </c>
       <c r="M7">
-        <v>0.2</v>
+        <v>0.26363636363636367</v>
       </c>
       <c r="N7">
-        <v>0.2</v>
+        <v>0.32727272727272727</v>
       </c>
       <c r="O7">
-        <v>0.2</v>
+        <v>0.39090909090909093</v>
       </c>
       <c r="P7">
-        <v>0.2</v>
+        <v>0.45454545454545459</v>
       </c>
       <c r="Q7">
-        <v>0.5</v>
+        <v>0.51818181818181819</v>
       </c>
       <c r="R7">
-        <v>0.5</v>
+        <v>0.58181818181818179</v>
       </c>
       <c r="S7">
-        <v>0.5</v>
+        <v>0.6454545454545455</v>
       </c>
       <c r="T7">
-        <v>0.5</v>
+        <v>0.70909090909090911</v>
       </c>
       <c r="U7">
-        <v>0.5</v>
+        <v>0.77272727272727282</v>
       </c>
       <c r="V7">
-        <v>0.5</v>
+        <v>0.83636363636363642</v>
       </c>
       <c r="W7">
         <v>0.9</v>
@@ -1316,34 +1316,34 @@
         <v>0.2</v>
       </c>
       <c r="M8">
-        <v>0.2</v>
+        <v>0.26363636363636367</v>
       </c>
       <c r="N8">
-        <v>0.2</v>
+        <v>0.32727272727272727</v>
       </c>
       <c r="O8">
-        <v>0.2</v>
+        <v>0.39090909090909093</v>
       </c>
       <c r="P8">
-        <v>0.2</v>
+        <v>0.45454545454545459</v>
       </c>
       <c r="Q8">
-        <v>0.5</v>
+        <v>0.51818181818181819</v>
       </c>
       <c r="R8">
-        <v>0.5</v>
+        <v>0.58181818181818179</v>
       </c>
       <c r="S8">
-        <v>0.5</v>
+        <v>0.6454545454545455</v>
       </c>
       <c r="T8">
-        <v>0.5</v>
+        <v>0.70909090909090911</v>
       </c>
       <c r="U8">
-        <v>0.5</v>
+        <v>0.77272727272727282</v>
       </c>
       <c r="V8">
-        <v>0.5</v>
+        <v>0.83636363636363642</v>
       </c>
       <c r="W8">
         <v>0.9</v>
@@ -1387,34 +1387,34 @@
         <v>0.2</v>
       </c>
       <c r="M9">
-        <v>0.2</v>
+        <v>0.26363636363636367</v>
       </c>
       <c r="N9">
-        <v>0.2</v>
+        <v>0.32727272727272727</v>
       </c>
       <c r="O9">
-        <v>0.2</v>
+        <v>0.39090909090909093</v>
       </c>
       <c r="P9">
-        <v>0.2</v>
+        <v>0.45454545454545459</v>
       </c>
       <c r="Q9">
-        <v>0.5</v>
+        <v>0.51818181818181819</v>
       </c>
       <c r="R9">
-        <v>0.5</v>
+        <v>0.58181818181818179</v>
       </c>
       <c r="S9">
-        <v>0.5</v>
+        <v>0.6454545454545455</v>
       </c>
       <c r="T9">
-        <v>0.5</v>
+        <v>0.70909090909090911</v>
       </c>
       <c r="U9">
-        <v>0.5</v>
+        <v>0.77272727272727282</v>
       </c>
       <c r="V9">
-        <v>0.5</v>
+        <v>0.83636363636363642</v>
       </c>
       <c r="W9">
         <v>0.9</v>
@@ -1458,34 +1458,34 @@
         <v>0.2</v>
       </c>
       <c r="M10">
-        <v>0.2</v>
+        <v>0.26363636363636367</v>
       </c>
       <c r="N10">
-        <v>0.2</v>
+        <v>0.32727272727272727</v>
       </c>
       <c r="O10">
-        <v>0.2</v>
+        <v>0.39090909090909093</v>
       </c>
       <c r="P10">
-        <v>0.2</v>
+        <v>0.45454545454545459</v>
       </c>
       <c r="Q10">
-        <v>0.5</v>
+        <v>0.51818181818181819</v>
       </c>
       <c r="R10">
-        <v>0.5</v>
+        <v>0.58181818181818179</v>
       </c>
       <c r="S10">
-        <v>0.5</v>
+        <v>0.6454545454545455</v>
       </c>
       <c r="T10">
-        <v>0.5</v>
+        <v>0.70909090909090911</v>
       </c>
       <c r="U10">
-        <v>0.5</v>
+        <v>0.77272727272727282</v>
       </c>
       <c r="V10">
-        <v>0.5</v>
+        <v>0.83636363636363642</v>
       </c>
       <c r="W10">
         <v>0.9</v>
@@ -1529,34 +1529,34 @@
         <v>0.2</v>
       </c>
       <c r="M11">
-        <v>0.2</v>
+        <v>0.26363636363636367</v>
       </c>
       <c r="N11">
-        <v>0.2</v>
+        <v>0.32727272727272727</v>
       </c>
       <c r="O11">
-        <v>0.2</v>
+        <v>0.39090909090909093</v>
       </c>
       <c r="P11">
-        <v>0.2</v>
+        <v>0.45454545454545459</v>
       </c>
       <c r="Q11">
-        <v>0.5</v>
+        <v>0.51818181818181819</v>
       </c>
       <c r="R11">
-        <v>0.5</v>
+        <v>0.58181818181818179</v>
       </c>
       <c r="S11">
-        <v>0.5</v>
+        <v>0.6454545454545455</v>
       </c>
       <c r="T11">
-        <v>0.5</v>
+        <v>0.70909090909090911</v>
       </c>
       <c r="U11">
-        <v>0.5</v>
+        <v>0.77272727272727282</v>
       </c>
       <c r="V11">
-        <v>0.5</v>
+        <v>0.83636363636363642</v>
       </c>
       <c r="W11">
         <v>0.9</v>
@@ -1600,34 +1600,34 @@
         <v>0.2</v>
       </c>
       <c r="M12">
-        <v>0.2</v>
+        <v>0.26363636363636367</v>
       </c>
       <c r="N12">
-        <v>0.2</v>
+        <v>0.32727272727272727</v>
       </c>
       <c r="O12">
-        <v>0.2</v>
+        <v>0.39090909090909093</v>
       </c>
       <c r="P12">
-        <v>0.2</v>
+        <v>0.45454545454545459</v>
       </c>
       <c r="Q12">
-        <v>0.5</v>
+        <v>0.51818181818181819</v>
       </c>
       <c r="R12">
-        <v>0.5</v>
+        <v>0.58181818181818179</v>
       </c>
       <c r="S12">
-        <v>0.5</v>
+        <v>0.6454545454545455</v>
       </c>
       <c r="T12">
-        <v>0.5</v>
+        <v>0.70909090909090911</v>
       </c>
       <c r="U12">
-        <v>0.5</v>
+        <v>0.77272727272727282</v>
       </c>
       <c r="V12">
-        <v>0.5</v>
+        <v>0.83636363636363642</v>
       </c>
       <c r="W12">
         <v>0.9</v>
@@ -1671,34 +1671,34 @@
         <v>0.2</v>
       </c>
       <c r="M13">
-        <v>0.2</v>
+        <v>0.26363636363636367</v>
       </c>
       <c r="N13">
-        <v>0.2</v>
+        <v>0.32727272727272727</v>
       </c>
       <c r="O13">
-        <v>0.2</v>
+        <v>0.39090909090909093</v>
       </c>
       <c r="P13">
-        <v>0.2</v>
+        <v>0.45454545454545459</v>
       </c>
       <c r="Q13">
-        <v>0.5</v>
+        <v>0.51818181818181819</v>
       </c>
       <c r="R13">
-        <v>0.5</v>
+        <v>0.58181818181818179</v>
       </c>
       <c r="S13">
-        <v>0.5</v>
+        <v>0.6454545454545455</v>
       </c>
       <c r="T13">
-        <v>0.5</v>
+        <v>0.70909090909090911</v>
       </c>
       <c r="U13">
-        <v>0.5</v>
+        <v>0.77272727272727282</v>
       </c>
       <c r="V13">
-        <v>0.5</v>
+        <v>0.83636363636363642</v>
       </c>
       <c r="W13">
         <v>0.9</v>

--- a/SType3.xlsx
+++ b/SType3.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://icrafcifor-my.sharepoint.com/personal/d_bodro_landscapealliance_org/Documents/Documents/GitHub/RegEco-PADAGIMO-SOLUSI/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="8_{8352FCB5-3818-471B-95EA-A95253910025}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{56F26C9E-5709-4ECA-B093-F76370F06E4D}"/>
+  <xr:revisionPtr revIDLastSave="8" documentId="8_{8352FCB5-3818-471B-95EA-A95253910025}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{351C7442-0332-4E7E-B2F5-94B0D7CF090D}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{BCA274C9-EF1D-4263-A604-C30810D98A49}"/>
   </bookViews>
@@ -778,7 +778,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04A98039-D7EE-467B-AECA-2C919B69B7D3}">
-  <dimension ref="A1:W13"/>
+  <dimension ref="A1:W16"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:23" x14ac:dyDescent="0.3">
@@ -1701,6 +1701,219 @@
         <v>0.83636363636363642</v>
       </c>
       <c r="W13">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A14">
+        <v>19</v>
+      </c>
+      <c r="B14">
+        <v>29</v>
+      </c>
+      <c r="C14">
+        <v>0</v>
+      </c>
+      <c r="D14">
+        <v>0</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
+      <c r="F14">
+        <v>0</v>
+      </c>
+      <c r="G14">
+        <v>0.1</v>
+      </c>
+      <c r="H14">
+        <v>0.1</v>
+      </c>
+      <c r="I14">
+        <v>0.1</v>
+      </c>
+      <c r="J14">
+        <v>0.1</v>
+      </c>
+      <c r="K14">
+        <v>0.1</v>
+      </c>
+      <c r="L14">
+        <v>0.2</v>
+      </c>
+      <c r="M14">
+        <v>0.26363636363636367</v>
+      </c>
+      <c r="N14">
+        <v>0.32727272727272727</v>
+      </c>
+      <c r="O14">
+        <v>0.39090909090909093</v>
+      </c>
+      <c r="P14">
+        <v>0.45454545454545459</v>
+      </c>
+      <c r="Q14">
+        <v>0.51818181818181819</v>
+      </c>
+      <c r="R14">
+        <v>0.58181818181818179</v>
+      </c>
+      <c r="S14">
+        <v>0.6454545454545455</v>
+      </c>
+      <c r="T14">
+        <v>0.70909090909090911</v>
+      </c>
+      <c r="U14">
+        <v>0.77272727272727282</v>
+      </c>
+      <c r="V14">
+        <v>0.83636363636363642</v>
+      </c>
+      <c r="W14">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A15">
+        <v>19</v>
+      </c>
+      <c r="B15">
+        <v>52</v>
+      </c>
+      <c r="C15">
+        <v>0</v>
+      </c>
+      <c r="D15">
+        <v>0</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
+      <c r="F15">
+        <v>0</v>
+      </c>
+      <c r="G15">
+        <v>0.1</v>
+      </c>
+      <c r="H15">
+        <v>0.1</v>
+      </c>
+      <c r="I15">
+        <v>0.1</v>
+      </c>
+      <c r="J15">
+        <v>0.1</v>
+      </c>
+      <c r="K15">
+        <v>0.1</v>
+      </c>
+      <c r="L15">
+        <v>0.2</v>
+      </c>
+      <c r="M15">
+        <v>0.26363636363636367</v>
+      </c>
+      <c r="N15">
+        <v>0.32727272727272727</v>
+      </c>
+      <c r="O15">
+        <v>0.39090909090909093</v>
+      </c>
+      <c r="P15">
+        <v>0.45454545454545459</v>
+      </c>
+      <c r="Q15">
+        <v>0.51818181818181819</v>
+      </c>
+      <c r="R15">
+        <v>0.58181818181818179</v>
+      </c>
+      <c r="S15">
+        <v>0.6454545454545455</v>
+      </c>
+      <c r="T15">
+        <v>0.70909090909090911</v>
+      </c>
+      <c r="U15">
+        <v>0.77272727272727282</v>
+      </c>
+      <c r="V15">
+        <v>0.83636363636363642</v>
+      </c>
+      <c r="W15">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A16">
+        <v>21</v>
+      </c>
+      <c r="B16">
+        <v>30</v>
+      </c>
+      <c r="C16">
+        <v>0</v>
+      </c>
+      <c r="D16">
+        <v>0</v>
+      </c>
+      <c r="E16">
+        <v>0</v>
+      </c>
+      <c r="F16">
+        <v>0</v>
+      </c>
+      <c r="G16">
+        <v>0.1</v>
+      </c>
+      <c r="H16">
+        <v>0.1</v>
+      </c>
+      <c r="I16">
+        <v>0.1</v>
+      </c>
+      <c r="J16">
+        <v>0.1</v>
+      </c>
+      <c r="K16">
+        <v>0.1</v>
+      </c>
+      <c r="L16">
+        <v>0.2</v>
+      </c>
+      <c r="M16">
+        <v>0.26363636363636367</v>
+      </c>
+      <c r="N16">
+        <v>0.32727272727272727</v>
+      </c>
+      <c r="O16">
+        <v>0.39090909090909093</v>
+      </c>
+      <c r="P16">
+        <v>0.45454545454545459</v>
+      </c>
+      <c r="Q16">
+        <v>0.51818181818181819</v>
+      </c>
+      <c r="R16">
+        <v>0.58181818181818179</v>
+      </c>
+      <c r="S16">
+        <v>0.6454545454545455</v>
+      </c>
+      <c r="T16">
+        <v>0.70909090909090911</v>
+      </c>
+      <c r="U16">
+        <v>0.77272727272727282</v>
+      </c>
+      <c r="V16">
+        <v>0.83636363636363642</v>
+      </c>
+      <c r="W16">
         <v>0.9</v>
       </c>
     </row>
